--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="575">
   <si>
     <t>Property</t>
   </si>
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241025120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1730,6 +1730,12 @@
   </si>
   <si>
     <t>Urgences pédiatriques</t>
+  </si>
+  <si>
+    <t>SST27</t>
+  </si>
+  <si>
+    <t>Innovation et recherche en sciences biologiques et pharmaceutiques</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R359-SurspecialiteTransversale/FHIR/TRE-R359-SurspecialiteTransversale</t>
@@ -2057,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2282,18 +2288,26 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>234</v>
+        <v>569</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>234</v>
+        <v>570</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="B29" t="s" s="2">
-        <v>569</v>
+      <c r="B30" t="s" s="2">
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -2320,10 +2334,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3">
@@ -2339,7 +2353,7 @@
         <v>235</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
   </sheetData>
